--- a/results/answer_card.xlsx
+++ b/results/answer_card.xlsx
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小莫雷兹 约翰逊</t>
+          <t>汉内斯 施泰因巴赫</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>卡梅隆 卡尔</t>
+          <t>小莫雷兹 约翰逊</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>汉内斯 施泰因巴赫</t>
+          <t>克里斯蒂安 安德森</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>克里斯蒂安 安德森</t>
+          <t>卡梅隆 卡尔</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>马利克 托马斯</t>
+          <t>本内特 斯特茨</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>泰勒 比洛多</t>
+          <t>阿伦 格雷夫斯</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>本内特 斯特茨</t>
+          <t>泰勒 比洛多</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>亚历克斯 卡拉班</t>
+          <t>亨利 维萨尔</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>马利奇 布朗</t>
+          <t>马利克 托马斯</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>亨利 维萨尔</t>
+          <t>亚历克斯 卡拉班</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>祖比 埃吉奥福尔</t>
+          <t>马利奇 布朗</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/results/answer_card.xlsx
+++ b/results/answer_card.xlsx
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>达柳斯 阿卡夫</t>
+          <t>纳撒尼尔 阿门特</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>纳撒尼尔 阿门特</t>
+          <t>达柳斯 阿卡夫</t>
         </is>
       </c>
     </row>

--- a/results/answer_card.xlsx
+++ b/results/answer_card.xlsx
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>纳撒尼尔 阿门特</t>
+          <t>迈克尔 布朗</t>
         </is>
       </c>
     </row>

--- a/results/answer_card.xlsx
+++ b/results/answer_card.xlsx
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小拉巴伦 菲隆</t>
+          <t>阿达伊 马拉</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>阿达伊 马拉</t>
+          <t>布雷登 伯里斯</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>汉内斯 施泰因巴赫</t>
+          <t>小莫雷兹 约翰逊</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>以赛亚 埃文斯</t>
+          <t>小拉巴伦 菲隆</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小莫雷兹 约翰逊</t>
+          <t>汉内斯 施泰因巴赫</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>克里斯蒂安 安德森</t>
+          <t>卡里姆 洛佩兹</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>卡梅隆 卡尔</t>
+          <t>克里斯蒂安 安德森</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>克里斯 塞纳克</t>
+          <t>阿伦 格雷夫斯</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>阿伦 格雷夫斯</t>
+          <t>克里斯 塞纳克</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>泰勒 比洛多</t>
+          <t>以赛亚 埃文斯</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>亚历克斯 卡拉班</t>
+          <t>乔舒亚 杰弗森</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>莱恩 康韦尔</t>
+          <t>卡梅隆 卡尔</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>马利奇 布朗</t>
+          <t>塞尔吉奥 德拉雷亚</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>布雷登 伯里斯</t>
+          <t>泰勒 比洛多</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
